--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96261</v>
+        <v>96277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96289</v>
+        <v>96311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96311</v>
+        <v>96315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96321</v>
+        <v>96328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96328</v>
+        <v>96333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113375583</v>
       </c>
       <c r="B3" t="n">
-        <v>96333</v>
+        <v>96361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90903809</v>
+        <v>127800297</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skoghem, Vg</t>
+          <t>Bollebygd, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>358311.8335343588</v>
+        <v>358105</v>
       </c>
       <c r="R2" t="n">
-        <v>6392935.86151462</v>
+        <v>6393039</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113375583</v>
+        <v>114002968</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,41 +793,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lönåsen, Vg</t>
+          <t>Bollebygd, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>358316</v>
+        <v>358189</v>
       </c>
       <c r="R3" t="n">
-        <v>6392775</v>
+        <v>6393085</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4 blommande plantor på 15 m.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,15 +889,408 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129949582</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>358191</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6393086</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129949590</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>358204</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6393072</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>90903809</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skoghem, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>358312</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6392936</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113375583</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lönåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>358316</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6392775</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Tim Hipkiss</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Tim Hipkiss</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30785-2023 artfynd.xlsx
+++ b/artfynd/A 30785-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127800297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114002968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949582</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949590</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903809</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,8 +1321,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113375583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>